--- a/source_data/SourceData_EDFig3.xlsx
+++ b/source_data/SourceData_EDFig3.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -573,6 +574,42 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>panel e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (limit_sweep, isothermal); published reactor-inlet compositions in analysis/meoh_literature_inversion_2026_10_05/inlet_inert_literature.csv</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>constants drawn on panel e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -585,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -724,7 +761,7 @@
         <v>0.14</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -735,7 +772,7 @@
         <v>0.16</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -746,7 +783,7 @@
         <v>0.18</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -757,7 +794,7 @@
         <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -768,7 +805,7 @@
         <v>0.22</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -779,7 +816,7 @@
         <v>0.24</v>
       </c>
       <c r="C15" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -790,7 +827,7 @@
         <v>0.26</v>
       </c>
       <c r="C16" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -801,7 +838,7 @@
         <v>0.28</v>
       </c>
       <c r="C17" t="n">
-        <v>298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -812,7 +849,7 @@
         <v>0.3</v>
       </c>
       <c r="C18" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -823,7 +860,7 @@
         <v>0.32</v>
       </c>
       <c r="C19" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -834,7 +871,7 @@
         <v>0.34</v>
       </c>
       <c r="C20" t="n">
-        <v>713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -845,7 +882,7 @@
         <v>0.36</v>
       </c>
       <c r="C21" t="n">
-        <v>850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -856,7 +893,7 @@
         <v>0.38</v>
       </c>
       <c r="C22" t="n">
-        <v>950</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -867,7 +904,7 @@
         <v>0.4</v>
       </c>
       <c r="C23" t="n">
-        <v>918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -878,7 +915,7 @@
         <v>0.42</v>
       </c>
       <c r="C24" t="n">
-        <v>1048</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -889,7 +926,7 @@
         <v>0.44</v>
       </c>
       <c r="C25" t="n">
-        <v>852</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -900,7 +937,7 @@
         <v>0.46</v>
       </c>
       <c r="C26" t="n">
-        <v>772</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -911,7 +948,7 @@
         <v>0.48</v>
       </c>
       <c r="C27" t="n">
-        <v>649</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -922,7 +959,7 @@
         <v>0.5</v>
       </c>
       <c r="C28" t="n">
-        <v>470</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -933,7 +970,7 @@
         <v>0.52</v>
       </c>
       <c r="C29" t="n">
-        <v>403</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30">
@@ -944,7 +981,7 @@
         <v>0.54</v>
       </c>
       <c r="C30" t="n">
-        <v>227</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31">
@@ -955,7 +992,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>169</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +1003,7 @@
         <v>0.58</v>
       </c>
       <c r="C32" t="n">
-        <v>84</v>
+        <v>509</v>
       </c>
     </row>
     <row r="33">
@@ -977,7 +1014,7 @@
         <v>0.6</v>
       </c>
       <c r="C33" t="n">
-        <v>56</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34">
@@ -988,7 +1025,7 @@
         <v>0.62</v>
       </c>
       <c r="C34" t="n">
-        <v>31</v>
+        <v>898</v>
       </c>
     </row>
     <row r="35">
@@ -999,7 +1036,7 @@
         <v>0.64</v>
       </c>
       <c r="C35" t="n">
-        <v>16</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="36">
@@ -1010,7 +1047,7 @@
         <v>0.66</v>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="37">
@@ -1021,7 +1058,7 @@
         <v>0.68</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>998</v>
       </c>
     </row>
     <row r="38">
@@ -1032,7 +1069,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1080,7 @@
         <v>0.72</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="40">
@@ -1054,7 +1091,7 @@
         <v>0.74</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>683</v>
       </c>
     </row>
     <row r="41">
@@ -1065,7 +1102,7 @@
         <v>0.76</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="42">
@@ -1076,7 +1113,7 @@
         <v>0.78</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43">
@@ -1087,7 +1124,7 @@
         <v>0.8</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46">
@@ -1123,7 +1160,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3975903614457831</v>
+        <v>0.6585365853658537</v>
       </c>
     </row>
     <row r="50">
@@ -1134,7 +1171,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0.236842, 0.550562</t>
+          <t>0.514844, 0.8</t>
         </is>
       </c>
     </row>
@@ -1146,6 +1183,16 @@
       </c>
       <c r="B51" t="n">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1234,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>0.39759</v>
+        <v>0.658537</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -1248,13 +1295,13 @@
         <v>0.001</v>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C5" t="n">
-        <v>0.39759</v>
+        <v>0.6463410000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -1262,13 +1309,13 @@
         <v>0.005</v>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C6" t="n">
-        <v>0.325301</v>
+        <v>0.634146</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -1276,13 +1323,13 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>0.277108</v>
+        <v>0.621951</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -1290,13 +1337,13 @@
         <v>0.02</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>0.192771</v>
+        <v>0.609756</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -1304,13 +1351,13 @@
         <v>0.05</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>0.108434</v>
+        <v>0.560976</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -1318,13 +1365,13 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0481928</v>
+        <v>0.512195</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1338,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1445,25 +1492,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37.3245</v>
+        <v>54.045</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
-        <v>13.368</v>
+        <v>12.067</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>17.02499999999986</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -1478,25 +1525,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39.3005</v>
+        <v>54.7785</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>22.3775</v>
+        <v>21.2175</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -1511,25 +1558,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41.1935</v>
+        <v>55.078</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>34.085</v>
+        <v>33.5735</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -1544,25 +1591,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38.498</v>
+        <v>55.5855</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>22.8355</v>
+        <v>23.1425</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="n">
         <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -1598,7 +1645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -1609,6 +1656,16 @@
       </c>
       <c r="B14" t="n">
         <v>2000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1622,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1710,34 +1767,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1016/j.apcata.2019.117144 | 40 bar | H2/CO2 4 | 52 NL/g/h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1016/j.apcata.2019.117144</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.81543</v>
+        <v>1.6901</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1746,16 +1803,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5754629999999999</v>
+        <v>1.57562</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9895</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9495</v>
+        <v>0.993</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1764,25 +1821,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1039/d0gc01597k | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1039/d0gc01597k</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.167776</v>
+        <v>1.28646</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9805</v>
+        <v>0.971</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1791,61 +1848,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 4 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0585352</v>
+        <v>1.25252</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.796</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0501515</v>
+        <v>1.10831</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9785</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1854,16 +1911,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.035436</v>
+        <v>1.08781</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.965</v>
+        <v>0.984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8675</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1872,223 +1929,223 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+          <t>10.1016/j.fuel.2022.125878 | 30 bar | H2/CO2 3 | 12000 h-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
+          <t>10.1016/j.fuel.2022.125878</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0209238</v>
+        <v>1.0199</v>
       </c>
       <c r="D10" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9435</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.804</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8985</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1016/j.cej.2024.149370 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1016/j.cej.2024.149370</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.14716</v>
+        <v>0.994806</v>
       </c>
       <c r="D11" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.785</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9935</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24000 h-1</t>
+          <t>10.1016/j.mcat.2020.111105 | 30 bar | H2/CO2 3 | 10000 h-1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376</t>
+          <t>10.1016/j.mcat.2020.111105</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0993523</v>
+        <v>0.975586</v>
       </c>
       <c r="D12" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.957</v>
+        <v>0.996</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9275</v>
+        <v>0.9645</v>
       </c>
       <c r="G12" t="n">
-        <v>0.926</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 20 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290</t>
+          <t>10.1016/j.jes.2023.05.010</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0394494</v>
+        <v>0.849194</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9935</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9365</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8665</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049</t>
+          <t>10.1126/sciadv.aaz2060</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0138626</v>
+        <v>0.831378</v>
       </c>
       <c r="D14" t="n">
-        <v>0.983</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9055</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8225</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.981</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 6 NL/g/h</t>
+          <t>10.1002/ente.201800747 | 40 bar | H2/CO2 3 | 21.6 NL/g/h</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682</t>
+          <t>10.1002/ente.201800747</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.09021129999999999</v>
+        <v>0.829407</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9695</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4415</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.673</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1016/j.mcat.2020.111105 | 30 bar | H2/CO2 3 | 10000 h-1</t>
+          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.1016/j.mcat.2020.111105</t>
+          <t>10.1126/sciadv.1701290</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0869496</v>
+        <v>0.5083259999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9385</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.819</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.743</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.86</v>
+        <v>0.964</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24000 h-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984</t>
+          <t>10.1016/j.fuel.2023.128376</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0175229</v>
+        <v>0.501371</v>
       </c>
       <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.9245</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.927</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1126/sciadv.1701290 | 20 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2097,46 +2154,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.017908</v>
+        <v>0.477993</v>
       </c>
       <c r="D18" t="n">
-        <v>0.924</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7895</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.619</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.728</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 12 NL/g/h</t>
+          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682</t>
+          <t>10.1016/j.fuel.2023.128376</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0412279</v>
+        <v>0.380904</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8995</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6125</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3445</v>
+        <v>0.999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6025</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2151,424 +2208,424 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0220533</v>
+        <v>0.364283</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8885</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.791</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.755</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8885</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 9 NL/g/h</t>
+          <t>10.1021/acsaem.1c01502 | 50 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682</t>
+          <t>10.1021/acsaem.1c01502</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0439352</v>
+        <v>0.352455</v>
       </c>
       <c r="D21" t="n">
-        <v>0.866</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5795</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.302</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5415</v>
+        <v>0.9845</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1126/sciadv.aaz2060</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0103981</v>
+        <v>0.335596</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8235</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.678</v>
+        <v>0.971</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5765</v>
+        <v>0.836</v>
       </c>
       <c r="G22" t="n">
-        <v>0.805</v>
+        <v>0.8695000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1039/c5ra04774a | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1016/j.apcata.2018.04.036 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.1039/c5ra04774a</t>
+          <t>10.1016/j.apcata.2018.04.036</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.00128524</v>
+        <v>0.279156</v>
       </c>
       <c r="D23" t="n">
-        <v>0.801</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.774</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.703</v>
+        <v>0.9145</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7065</v>
+        <v>0.9055</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18 NL/g/h</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e</t>
+          <t>10.1016/j.jes.2023.05.010</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0123021</v>
+        <v>0.26376</v>
       </c>
       <c r="D24" t="n">
-        <v>0.787</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5945</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5365</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7775</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.1002/cctc.202000974</t>
+          <t>10.1126/sciadv.1701290</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.008536200000000001</v>
+        <v>0.259628</v>
       </c>
       <c r="D25" t="n">
-        <v>0.776</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.649</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5225</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.739</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 16 NL/g/h</t>
+          <t>10.1038/s41467-021-22224-x | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5b00682</t>
+          <t>10.1038/s41467-021-22224-x</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0432266</v>
+        <v>0.217273</v>
       </c>
       <c r="D26" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6445</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.506</v>
+        <v>0.992</v>
       </c>
       <c r="G26" t="n">
-        <v>0.674</v>
+        <v>0.9025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.127927</t>
+          <t>10.1016/j.fuel.2024.131111</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.00332237</v>
+        <v>0.176094</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7445000000000001</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.655</v>
+        <v>0.997</v>
       </c>
       <c r="F27" t="n">
-        <v>0.57</v>
+        <v>0.8055</v>
       </c>
       <c r="G27" t="n">
-        <v>0.49</v>
+        <v>0.8215</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+          <t>10.1016/j.jcat.2016.03.017 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1016/j.jcat.2016.03.017</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0199457</v>
+        <v>0.159201</v>
       </c>
       <c r="D28" t="n">
-        <v>0.728</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5649999999999999</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4685</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.551</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290</t>
+          <t>10.1021/acscatal.9b03305</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0021168</v>
+        <v>0.144612</v>
       </c>
       <c r="D29" t="n">
-        <v>0.722</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.701</v>
+        <v>0.999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.991</v>
       </c>
       <c r="G29" t="n">
-        <v>0.579</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376</t>
+          <t>10.1021/acs.iecr.7b01464</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.00730798</v>
+        <v>0.136346</v>
       </c>
       <c r="D30" t="n">
-        <v>0.718</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6885</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.9665</v>
       </c>
       <c r="G30" t="n">
-        <v>0.737</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.00625915</v>
+        <v>0.133089</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6919999999999999</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.703</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6825</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1016/j.jcou.2022.102209 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1021/cs500979c | 80 bar | H2/CO2 3 | 3600 h-1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.1016/j.jcou.2022.102209</t>
+          <t>10.1021/cs500979c</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0104783</v>
+        <v>0.095912</v>
       </c>
       <c r="D32" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5495</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5755</v>
+        <v>0.9225</v>
       </c>
       <c r="G32" t="n">
-        <v>0.484</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.1002/anie.202401168 | 30 bar | H2/CO2 3 | 9 NL/g/h</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.1002/anie.202401168</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.00350671</v>
+        <v>0.0932558</v>
       </c>
       <c r="D33" t="n">
-        <v>0.616</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.589</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5105</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.509</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 0.25 | 24000 h-1</t>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b01869</t>
+          <t>10.1039/c6ra28305e</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.00494321</v>
+        <v>0.0264893</v>
       </c>
       <c r="D34" t="n">
-        <v>0.536</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3545</v>
+        <v>0.978</v>
       </c>
       <c r="F34" t="n">
-        <v>0.274</v>
+        <v>0.8445</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3055</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2024.131111 | 60 bar | H2/CO2 10 | 116 NL/g/h</t>
+          <t>10.1021/acscatal.0c05628 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2024.131111</t>
+          <t>10.1021/acscatal.0c05628</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.00220068</v>
+        <v>0.666845</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5125</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.496</v>
+        <v>0.975</v>
       </c>
       <c r="F35" t="n">
-        <v>0.485</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.487</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="36">
@@ -2583,19 +2640,1071 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008735450000000001</v>
+        <v>0.627734</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2845</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3305</v>
+        <v>0.9895</v>
       </c>
       <c r="F36" t="n">
-        <v>0.39</v>
+        <v>0.928</v>
       </c>
       <c r="G36" t="n">
-        <v>0.338</v>
+        <v>0.9795</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10.1002/anie.202401168 | 30 bar | H2/CO2 3 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10.1002/anie.202401168</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.528884</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.921</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.549488</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.216698</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9415</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.8975</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 16 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5b00682</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>3.72737</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.887</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2.9939</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.9935</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0817657</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcou.2022.102209 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcou.2022.102209</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1.00804</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.926</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.01152</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.8015</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.526</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2012.05.020</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.376425</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.9765</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6805</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.9715</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcatb.2017.06.069 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcatb.2017.06.069</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.448368</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.9705</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.7805</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.864</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.12945</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.9435</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.947</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10.1021/acsami.1c05586 | 30 bar | H2/CO2 3 | 7.2 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10.1021/acsami.1c05586</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2.0512</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6145</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2019.05.040 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2019.05.040</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.275299</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.9285</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.7875</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.916</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0274762</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.7385</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.8535</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10.1039/c5ra04774a | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10.1039/c5ra04774a</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.08487260000000001</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.8035</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8685</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.0c03324 | 30 bar | H2/CO2 3 | 6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.0c03324</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.158936</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.5955</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.476</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.00633792</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.6445</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.0c03324 | 30 bar | H2/CO2 3 | 14 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.0c03324</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0449574</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.513</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.0202078</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.5365</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111 | 60 bar | H2/CO2 10 | 116 NL/g/h</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.00393752</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5315</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.000856731</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>panel e</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (limit_sweep, isothermal); published reactor-inlet compositions in analysis/meoh_literature_inversion_2026_10_05/inlet_inert_literature.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>limit</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>mismatched</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>iso_groups</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>iso_mismatched</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>iso_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>79</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6835443037974683</v>
+      </c>
+      <c r="F4" t="n">
+        <v>163</v>
+      </c>
+      <c r="G4" t="n">
+        <v>59</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3619631901840491</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>79</v>
+      </c>
+      <c r="D5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6582278481012658</v>
+      </c>
+      <c r="F5" t="n">
+        <v>168</v>
+      </c>
+      <c r="G5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3511904761904762</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="F6" t="n">
+        <v>170</v>
+      </c>
+      <c r="G6" t="n">
+        <v>63</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3705882352941177</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.06862515529373837</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>reference loop 6.86%</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>82</v>
+      </c>
+      <c r="D7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6585365853658537</v>
+      </c>
+      <c r="F7" t="n">
+        <v>170</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>83</v>
+      </c>
+      <c r="D8" t="n">
+        <v>54</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6506024096385542</v>
+      </c>
+      <c r="F8" t="n">
+        <v>170</v>
+      </c>
+      <c r="G8" t="n">
+        <v>59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3470588235294118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>83</v>
+      </c>
+      <c r="D9" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5783132530120482</v>
+      </c>
+      <c r="F9" t="n">
+        <v>170</v>
+      </c>
+      <c r="G9" t="n">
+        <v>54</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3176470588235294</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>83</v>
+      </c>
+      <c r="D10" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5542168674698795</v>
+      </c>
+      <c r="F10" t="n">
+        <v>170</v>
+      </c>
+      <c r="G10" t="n">
+        <v>55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>83</v>
+      </c>
+      <c r="D11" t="n">
+        <v>39</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4698795180722892</v>
+      </c>
+      <c r="F11" t="n">
+        <v>170</v>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2823529411764706</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>83</v>
+      </c>
+      <c r="D12" t="n">
+        <v>41</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4939759036144578</v>
+      </c>
+      <c r="F12" t="n">
+        <v>170</v>
+      </c>
+      <c r="G12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2411764705882353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>83</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4698795180722892</v>
+      </c>
+      <c r="F13" t="n">
+        <v>170</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2235294117647059</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>83</v>
+      </c>
+      <c r="D14" t="n">
+        <v>37</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4457831325301205</v>
+      </c>
+      <c r="F14" t="n">
+        <v>170</v>
+      </c>
+      <c r="G14" t="n">
+        <v>36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2117647058823529</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v/>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>83</v>
+      </c>
+      <c r="D15" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4216867469879518</v>
+      </c>
+      <c r="F15" t="n">
+        <v>170</v>
+      </c>
+      <c r="G15" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>constants drawn on panel e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.06862515529373837</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>literature</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.0492, 0.10249, 4</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig3.xlsx
+++ b/source_data/SourceData_EDFig3.xlsx
@@ -12,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -574,42 +573,6 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>panel e</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (limit_sweep, isothermal); published reactor-inlet compositions in analysis/meoh_literature_inversion_2026_10_05/inlet_inert_literature.csv</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>constants drawn on panel e</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -622,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -761,7 +724,7 @@
         <v>0.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -772,7 +735,7 @@
         <v>0.16</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -783,7 +746,7 @@
         <v>0.18</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -794,7 +757,7 @@
         <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -805,7 +768,7 @@
         <v>0.22</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -816,7 +779,7 @@
         <v>0.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16">
@@ -827,7 +790,7 @@
         <v>0.26</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +801,7 @@
         <v>0.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +812,7 @@
         <v>0.3</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19">
@@ -860,7 +823,7 @@
         <v>0.32</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +834,7 @@
         <v>0.34</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>713</v>
       </c>
     </row>
     <row r="21">
@@ -882,7 +845,7 @@
         <v>0.36</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
     </row>
     <row r="22">
@@ -893,7 +856,7 @@
         <v>0.38</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>950</v>
       </c>
     </row>
     <row r="23">
@@ -904,7 +867,7 @@
         <v>0.4</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>918</v>
       </c>
     </row>
     <row r="24">
@@ -915,7 +878,7 @@
         <v>0.42</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="25">
@@ -926,7 +889,7 @@
         <v>0.44</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>852</v>
       </c>
     </row>
     <row r="26">
@@ -937,7 +900,7 @@
         <v>0.46</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>772</v>
       </c>
     </row>
     <row r="27">
@@ -948,7 +911,7 @@
         <v>0.48</v>
       </c>
       <c r="C27" t="n">
-        <v>44</v>
+        <v>649</v>
       </c>
     </row>
     <row r="28">
@@ -959,7 +922,7 @@
         <v>0.5</v>
       </c>
       <c r="C28" t="n">
-        <v>63</v>
+        <v>470</v>
       </c>
     </row>
     <row r="29">
@@ -970,7 +933,7 @@
         <v>0.52</v>
       </c>
       <c r="C29" t="n">
-        <v>150</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30">
@@ -981,7 +944,7 @@
         <v>0.54</v>
       </c>
       <c r="C30" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31">
@@ -992,7 +955,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>340</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +966,7 @@
         <v>0.58</v>
       </c>
       <c r="C32" t="n">
-        <v>509</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
@@ -1014,7 +977,7 @@
         <v>0.6</v>
       </c>
       <c r="C33" t="n">
-        <v>629</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
@@ -1025,7 +988,7 @@
         <v>0.62</v>
       </c>
       <c r="C34" t="n">
-        <v>898</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35">
@@ -1036,7 +999,7 @@
         <v>0.64</v>
       </c>
       <c r="C35" t="n">
-        <v>1016</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1047,7 +1010,7 @@
         <v>0.66</v>
       </c>
       <c r="C36" t="n">
-        <v>1131</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1058,7 +1021,7 @@
         <v>0.68</v>
       </c>
       <c r="C37" t="n">
-        <v>998</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1069,7 +1032,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>1053</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1080,7 +1043,7 @@
         <v>0.72</v>
       </c>
       <c r="C39" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1091,7 +1054,7 @@
         <v>0.74</v>
       </c>
       <c r="C40" t="n">
-        <v>683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1102,7 +1065,7 @@
         <v>0.76</v>
       </c>
       <c r="C41" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1113,7 +1076,7 @@
         <v>0.78</v>
       </c>
       <c r="C42" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1124,7 +1087,7 @@
         <v>0.8</v>
       </c>
       <c r="C43" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1160,7 +1123,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.3975903614457831</v>
       </c>
     </row>
     <row r="50">
@@ -1171,7 +1134,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0.514844, 0.8</t>
+          <t>0.236842, 0.550562</t>
         </is>
       </c>
     </row>
@@ -1183,16 +1146,6 @@
       </c>
       <c r="B51" t="n">
         <v>10000</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1281,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>0.658537</v>
+        <v>0.39759</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -1295,13 +1248,13 @@
         <v>0.001</v>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6463410000000001</v>
+        <v>0.39759</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -1309,13 +1262,13 @@
         <v>0.005</v>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>0.634146</v>
+        <v>0.325301</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1323,13 +1276,13 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>0.621951</v>
+        <v>0.277108</v>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1337,13 +1290,13 @@
         <v>0.02</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>0.609756</v>
+        <v>0.192771</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1351,13 +1304,13 @@
         <v>0.05</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>0.560976</v>
+        <v>0.108434</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1365,13 +1318,13 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.512195</v>
+        <v>0.0481928</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1385,7 +1338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1492,25 +1445,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.045</v>
+        <v>37.3245</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>12.067</v>
+        <v>13.368</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>17.02499999999986</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1525,25 +1478,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54.7785</v>
+        <v>39.3005</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>21.2175</v>
+        <v>22.3775</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1558,25 +1511,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.078</v>
+        <v>41.1935</v>
       </c>
       <c r="D6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" t="n">
         <v>49</v>
       </c>
-      <c r="E6" t="n">
-        <v>61</v>
-      </c>
       <c r="F6" t="n">
-        <v>33.5735</v>
+        <v>34.085</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1591,25 +1544,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>55.5855</v>
+        <v>38.498</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>23.1425</v>
+        <v>22.8355</v>
       </c>
       <c r="G7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
         <v>30</v>
       </c>
       <c r="I7" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1645,7 +1598,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -1656,16 +1609,6 @@
       </c>
       <c r="B14" t="n">
         <v>2000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1679,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1767,34 +1710,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2019.117144 | 40 bar | H2/CO2 4 | 52 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2019.117144</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.6901</v>
+        <v>1.81543</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1803,16 +1746,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.57562</v>
+        <v>0.5754629999999999</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.9895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.993</v>
+        <v>0.9495</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -1821,25 +1764,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1039/d0gc01597k | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1039/d0gc01597k</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.28646</v>
+        <v>0.167776</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.971</v>
+        <v>0.9805</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -1848,61 +1791,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 4 | 12 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.25252</v>
+        <v>0.0585352</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.966</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.10831</v>
+        <v>0.0501515</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9785</v>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9775</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1911,16 +1854,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.08781</v>
+        <v>0.035436</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.984</v>
+        <v>0.965</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8675</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1929,223 +1872,223 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2022.125878 | 30 bar | H2/CO2 3 | 12000 h-1</t>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2022.125878</t>
+          <t>10.1126/sciadv.aaz2060</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.0199</v>
+        <v>0.0209238</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.9435</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.804</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.8985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1016/j.cej.2024.149370 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1016/j.cej.2024.149370</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.994806</v>
+        <v>0.14716</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.785</v>
       </c>
       <c r="G11" t="n">
-        <v>0.988</v>
+        <v>0.9935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1016/j.mcat.2020.111105 | 30 bar | H2/CO2 3 | 10000 h-1</t>
+          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24000 h-1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.1016/j.mcat.2020.111105</t>
+          <t>10.1016/j.fuel.2023.128376</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.975586</v>
+        <v>0.0993523</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="E12" t="n">
-        <v>0.996</v>
+        <v>0.957</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9645</v>
+        <v>0.9275</v>
       </c>
       <c r="G12" t="n">
-        <v>0.953</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
+          <t>10.1126/sciadv.1701290 | 20 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010</t>
+          <t>10.1126/sciadv.1701290</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.849194</v>
+        <v>0.0394494</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.9935</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.9365</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
+          <t>10.1016/j.cattod.2020.05.049</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.831378</v>
+        <v>0.0138626</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.9055</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.8225</v>
       </c>
       <c r="G14" t="n">
-        <v>0.99</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1002/ente.201800747 | 40 bar | H2/CO2 3 | 21.6 NL/g/h</t>
+          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 6 NL/g/h</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.1002/ente.201800747</t>
+          <t>10.1021/acscatal.5b00682</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.829407</v>
+        <v>0.09021129999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.9695</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.4415</v>
       </c>
       <c r="G15" t="n">
-        <v>0.993</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1016/j.mcat.2020.111105 | 30 bar | H2/CO2 3 | 10000 h-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290</t>
+          <t>10.1016/j.mcat.2020.111105</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5083259999999999</v>
+        <v>0.0869496</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.9385</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.819</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.743</v>
       </c>
       <c r="G16" t="n">
-        <v>0.964</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24000 h-1</t>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376</t>
+          <t>10.1021/acscatal.5c05984</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.501371</v>
+        <v>0.0175229</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.9245</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9805</v>
+        <v>0.785</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9245</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 20 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2154,46 +2097,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.477993</v>
+        <v>0.017908</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.924</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.7895</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.619</v>
       </c>
       <c r="G18" t="n">
-        <v>0.988</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376</t>
+          <t>10.1021/acscatal.5b00682</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.380904</v>
+        <v>0.0412279</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.8995</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.6125</v>
       </c>
       <c r="F19" t="n">
-        <v>0.999</v>
+        <v>0.3445</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.6025</v>
       </c>
     </row>
     <row r="20">
@@ -2208,424 +2151,424 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.364283</v>
+        <v>0.0220533</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.8885</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.791</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.755</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0.8885</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1021/acsaem.1c01502 | 50 bar | H2/CO2 3 | 30 NL/g/h</t>
+          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.1021/acsaem.1c01502</t>
+          <t>10.1021/acscatal.5b00682</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.352455</v>
+        <v>0.0439352</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.866</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.5795</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.302</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9845</v>
+        <v>0.5415</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.335596</v>
+        <v>0.0103981</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.8235</v>
       </c>
       <c r="E22" t="n">
-        <v>0.971</v>
+        <v>0.678</v>
       </c>
       <c r="F22" t="n">
-        <v>0.836</v>
+        <v>0.5765</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.805</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2018.04.036 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+          <t>10.1039/c5ra04774a | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2018.04.036</t>
+          <t>10.1039/c5ra04774a</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.279156</v>
+        <v>0.00128524</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0.801</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.774</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9145</v>
+        <v>0.703</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9055</v>
+        <v>0.7065</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18 NL/g/h</t>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010</t>
+          <t>10.1039/c6ra28305e</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.26376</v>
+        <v>0.0123021</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0.787</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.5945</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.5365</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.7775</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290</t>
+          <t>10.1002/cctc.202000974</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.259628</v>
+        <v>0.008536200000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.776</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.649</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.5225</v>
       </c>
       <c r="G25" t="n">
-        <v>0.974</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1038/s41467-021-22224-x | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 16 NL/g/h</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.1038/s41467-021-22224-x</t>
+          <t>10.1021/acscatal.5b00682</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.217273</v>
+        <v>0.0432266</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0.76</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.6445</v>
       </c>
       <c r="F26" t="n">
-        <v>0.992</v>
+        <v>0.506</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9025</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2024.131111</t>
+          <t>10.1016/j.fuel.2023.127927</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.176094</v>
+        <v>0.00332237</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.997</v>
+        <v>0.655</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8055</v>
+        <v>0.57</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8215</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1016/j.jcat.2016.03.017 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.1016/j.jcat.2016.03.017</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.159201</v>
+        <v>0.0199457</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.728</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.4685</v>
       </c>
       <c r="G28" t="n">
-        <v>0.99</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305</t>
+          <t>10.1126/sciadv.1701290</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.144612</v>
+        <v>0.0021168</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.722</v>
       </c>
       <c r="E29" t="n">
-        <v>0.999</v>
+        <v>0.701</v>
       </c>
       <c r="F29" t="n">
-        <v>0.991</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.579</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464</t>
+          <t>10.1016/j.fuel.2023.128376</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.136346</v>
+        <v>0.00730798</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.718</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.6885</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9665</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.955</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1021/acscatal.9b03305</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.133089</v>
+        <v>0.00625915</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.703</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0.6825</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1021/cs500979c | 80 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>10.1016/j.jcou.2022.102209 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.1021/cs500979c</t>
+          <t>10.1016/j.jcou.2022.102209</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.095912</v>
+        <v>0.0104783</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.5495</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9225</v>
+        <v>0.5755</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+          <t>10.1002/anie.202401168 | 30 bar | H2/CO2 3 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1002/anie.202401168</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0932558</v>
+        <v>0.00350671</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0.616</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.589</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9955000000000001</v>
+        <v>0.5105</v>
       </c>
       <c r="G33" t="n">
-        <v>0.909</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 0.25 | 24000 h-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e</t>
+          <t>10.1021/acscatal.9b01869</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0264893</v>
+        <v>0.00494321</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0.536</v>
       </c>
       <c r="E34" t="n">
-        <v>0.978</v>
+        <v>0.3545</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8445</v>
+        <v>0.274</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0.3055</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.0c05628 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1016/j.fuel.2024.131111 | 60 bar | H2/CO2 10 | 116 NL/g/h</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.0c05628</t>
+          <t>10.1016/j.fuel.2024.131111</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.666845</v>
+        <v>0.00220068</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.5125</v>
       </c>
       <c r="E35" t="n">
-        <v>0.975</v>
+        <v>0.496</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.485</v>
       </c>
       <c r="G35" t="n">
-        <v>0.96</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="36">
@@ -2640,1071 +2583,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.627734</v>
+        <v>0.008735450000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.2845</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9895</v>
+        <v>0.3305</v>
       </c>
       <c r="F36" t="n">
-        <v>0.928</v>
+        <v>0.39</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9795</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>10.1002/anie.202401168 | 30 bar | H2/CO2 3 | 9 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10.1002/anie.202401168</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.528884</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.9855</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.921</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2020.05.049</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.549488</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.216698</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.9415</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.8975</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.9965000000000001</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 16 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5b00682</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3.72737</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.9965000000000001</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.9485</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.887</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2.9939</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.9065</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.9935</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5c05984</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.0817657</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcou.2022.102209 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcou.2022.102209</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1.00804</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.926</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 18 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0.01152</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.8015</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.5655</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.526</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcat.2012.05.020</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.376425</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.9765</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.6805</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.9715</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcatb.2017.06.069 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcatb.2017.06.069</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.448368</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.9705</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.8875</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.7805</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.864</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.12945</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.9435</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.7375</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.947</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>10.1021/acsami.1c05586 | 30 bar | H2/CO2 3 | 7.2 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>10.1021/acsami.1c05586</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2.0512</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.9405</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.6145</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2019.05.040 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2019.05.040</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.275299</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9285</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.7875</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.916</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2023.127927</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0274762</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.7385</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.8535</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>10.1039/c5ra04774a | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>10.1039/c5ra04774a</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.08487260000000001</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.8075</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.8035</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.8685</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324 | 30 bar | H2/CO2 3 | 6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.158936</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.6545</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.5955</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.476</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>10.1002/cctc.202000974</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.00633792</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.7035</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.6445</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324 | 30 bar | H2/CO2 3 | 14 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0449574</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.5145</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.513</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.0202078</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.5405</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.5365</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111 | 60 bar | H2/CO2 10 | 116 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.00393752</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.5315</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.5004999999999999</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 4000 h-1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.000856731</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.489</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>panel e</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (limit_sweep, isothermal); published reactor-inlet compositions in analysis/meoh_literature_inversion_2026_10_05/inlet_inert_literature.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>limit</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>mismatched</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>iso_groups</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>iso_mismatched</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>iso_share</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>79</v>
-      </c>
-      <c r="D4" t="n">
-        <v>54</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.6835443037974683</v>
-      </c>
-      <c r="F4" t="n">
-        <v>163</v>
-      </c>
-      <c r="G4" t="n">
-        <v>59</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.3619631901840491</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>79</v>
-      </c>
-      <c r="D5" t="n">
-        <v>52</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6582278481012658</v>
-      </c>
-      <c r="F5" t="n">
-        <v>168</v>
-      </c>
-      <c r="G5" t="n">
-        <v>59</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3511904761904762</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>80</v>
-      </c>
-      <c r="D6" t="n">
-        <v>54</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="F6" t="n">
-        <v>170</v>
-      </c>
-      <c r="G6" t="n">
-        <v>63</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.3705882352941177</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.06862515529373837</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>reference loop 6.86%</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>82</v>
-      </c>
-      <c r="D7" t="n">
-        <v>54</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.6585365853658537</v>
-      </c>
-      <c r="F7" t="n">
-        <v>170</v>
-      </c>
-      <c r="G7" t="n">
-        <v>60</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>83</v>
-      </c>
-      <c r="D8" t="n">
-        <v>54</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.6506024096385542</v>
-      </c>
-      <c r="F8" t="n">
-        <v>170</v>
-      </c>
-      <c r="G8" t="n">
-        <v>59</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.3470588235294118</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>83</v>
-      </c>
-      <c r="D9" t="n">
-        <v>48</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.5783132530120482</v>
-      </c>
-      <c r="F9" t="n">
-        <v>170</v>
-      </c>
-      <c r="G9" t="n">
-        <v>54</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.3176470588235294</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>83</v>
-      </c>
-      <c r="D10" t="n">
-        <v>46</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.5542168674698795</v>
-      </c>
-      <c r="F10" t="n">
-        <v>170</v>
-      </c>
-      <c r="G10" t="n">
-        <v>55</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.3235294117647059</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>83</v>
-      </c>
-      <c r="D11" t="n">
-        <v>39</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.4698795180722892</v>
-      </c>
-      <c r="F11" t="n">
-        <v>170</v>
-      </c>
-      <c r="G11" t="n">
-        <v>48</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.2823529411764706</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>83</v>
-      </c>
-      <c r="D12" t="n">
-        <v>41</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4939759036144578</v>
-      </c>
-      <c r="F12" t="n">
-        <v>170</v>
-      </c>
-      <c r="G12" t="n">
-        <v>41</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.2411764705882353</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>83</v>
-      </c>
-      <c r="D13" t="n">
-        <v>39</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4698795180722892</v>
-      </c>
-      <c r="F13" t="n">
-        <v>170</v>
-      </c>
-      <c r="G13" t="n">
-        <v>38</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.2235294117647059</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>83</v>
-      </c>
-      <c r="D14" t="n">
-        <v>37</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.4457831325301205</v>
-      </c>
-      <c r="F14" t="n">
-        <v>170</v>
-      </c>
-      <c r="G14" t="n">
-        <v>36</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.2117647058823529</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v/>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>83</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.4216867469879518</v>
-      </c>
-      <c r="F15" t="n">
-        <v>170</v>
-      </c>
-      <c r="G15" t="n">
-        <v>35</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.2058823529411765</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>constants drawn on panel e</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.06862515529373837</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>literature</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.0492, 0.10249, 4</t>
-        </is>
+        <v>0.338</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig3.xlsx
+++ b/source_data/SourceData_EDFig3.xlsx
@@ -706,7 +706,7 @@
         <v>0.04</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -728,7 +728,7 @@
         <v>0.08</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -750,7 +750,7 @@
         <v>0.12</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -761,7 +761,7 @@
         <v>0.14</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -772,7 +772,7 @@
         <v>0.16</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -783,7 +783,7 @@
         <v>0.18</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
@@ -794,7 +794,7 @@
         <v>0.2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14">
@@ -805,7 +805,7 @@
         <v>0.22</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15">
@@ -816,7 +816,7 @@
         <v>0.24</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16">
@@ -827,7 +827,7 @@
         <v>0.26</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17">
@@ -838,7 +838,7 @@
         <v>0.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18">
@@ -849,7 +849,7 @@
         <v>0.3</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
     </row>
     <row r="19">
@@ -860,7 +860,7 @@
         <v>0.32</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +871,7 @@
         <v>0.34</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21">
@@ -882,7 +882,7 @@
         <v>0.36</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>740</v>
       </c>
     </row>
     <row r="22">
@@ -893,7 +893,7 @@
         <v>0.38</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>638</v>
       </c>
     </row>
     <row r="23">
@@ -904,7 +904,7 @@
         <v>0.4</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24">
@@ -915,7 +915,7 @@
         <v>0.42</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25">
@@ -926,7 +926,7 @@
         <v>0.44</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>609</v>
       </c>
     </row>
     <row r="26">
@@ -937,7 +937,7 @@
         <v>0.46</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>551</v>
       </c>
     </row>
     <row r="27">
@@ -948,7 +948,7 @@
         <v>0.48</v>
       </c>
       <c r="C27" t="n">
-        <v>44</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28">
@@ -959,7 +959,7 @@
         <v>0.5</v>
       </c>
       <c r="C28" t="n">
-        <v>63</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29">
@@ -970,7 +970,7 @@
         <v>0.52</v>
       </c>
       <c r="C29" t="n">
-        <v>150</v>
+        <v>411</v>
       </c>
     </row>
     <row r="30">
@@ -981,7 +981,7 @@
         <v>0.54</v>
       </c>
       <c r="C30" t="n">
-        <v>215</v>
+        <v>305</v>
       </c>
     </row>
     <row r="31">
@@ -992,7 +992,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>340</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
         <v>0.58</v>
       </c>
       <c r="C32" t="n">
-        <v>509</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33">
@@ -1014,7 +1014,7 @@
         <v>0.6</v>
       </c>
       <c r="C33" t="n">
-        <v>629</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
@@ -1025,7 +1025,7 @@
         <v>0.62</v>
       </c>
       <c r="C34" t="n">
-        <v>898</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -1036,7 +1036,7 @@
         <v>0.64</v>
       </c>
       <c r="C35" t="n">
-        <v>1016</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -1047,7 +1047,7 @@
         <v>0.66</v>
       </c>
       <c r="C36" t="n">
-        <v>1131</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1058,7 +1058,7 @@
         <v>0.68</v>
       </c>
       <c r="C37" t="n">
-        <v>998</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -1069,7 +1069,7 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>1053</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1080,7 +1080,7 @@
         <v>0.72</v>
       </c>
       <c r="C39" t="n">
-        <v>810</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1091,7 +1091,7 @@
         <v>0.74</v>
       </c>
       <c r="C40" t="n">
-        <v>683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1102,7 +1102,7 @@
         <v>0.76</v>
       </c>
       <c r="C41" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1113,7 +1113,7 @@
         <v>0.78</v>
       </c>
       <c r="C42" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1124,7 +1124,7 @@
         <v>0.8</v>
       </c>
       <c r="C43" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="50">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0.514844, 0.8</t>
+          <t>0.151515, 0.571429</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.658537</v>
+        <v>0.375</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1295,13 +1295,13 @@
         <v>0.001</v>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6463410000000001</v>
+        <v>0.35</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1309,13 +1309,13 @@
         <v>0.005</v>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.634146</v>
+        <v>0.325</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1323,13 +1323,13 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>0.621951</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1337,13 +1337,13 @@
         <v>0.02</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>0.609756</v>
+        <v>0.2</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1351,13 +1351,13 @@
         <v>0.05</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0.560976</v>
+        <v>0.175</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1365,13 +1365,13 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.512195</v>
+        <v>0.15</v>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1385,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>54.045</v>
+        <v>16.486</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>12.067</v>
+        <v>4.208</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>17.02499999999986</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1525,25 +1525,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>54.7785</v>
+        <v>17.394</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>21.2175</v>
+        <v>8.000999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1558,114 +1558,81 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.078</v>
+        <v>17.988</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>33.5735</v>
+        <v>13.7175</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>meas_k1_plus_extraction</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>error x1 + plot-reading errors</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>55.5855</v>
-      </c>
-      <c r="D7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E7" t="n">
-        <v>61</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23.1425</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17</v>
-      </c>
-      <c r="H7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" t="n">
-        <v>40</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>constants drawn on panel c</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>constants drawn on panel c</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_main_result_stats_2026_10_06/summary.json</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/summary.json</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>draws</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>54</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>draws</t>
+          <t>groups</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1679,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1758,43 +1725,35 @@
           <t>p_mismatch_meas_k4</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>p_mismatch_meas_k1_plus_extraction</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2019.117144 | 40 bar | H2/CO2 4 | 52 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2019.117144</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.6901</v>
+        <v>0.828627</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1803,7 +1762,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.57562</v>
+        <v>0.57546</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1812,25 +1771,22 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1039/d0gc01597k | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1039/d0gc01597k</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.28646</v>
+        <v>0.167776</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -1839,25 +1795,22 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 4 | 12 NL/g/h</t>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1126/sciadv.aaz2060</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.25252</v>
+        <v>0.115626</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1866,43 +1819,37 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.966</v>
+        <v>0.9605</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.10831</v>
+        <v>0.0501492</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9775</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1911,1315 +1858,232 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.08781</v>
+        <v>0.0354367</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0.984</v>
+        <v>0.9885</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8675</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2022.125878 | 30 bar | H2/CO2 3 | 12000 h-1</t>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2022.125878</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.0199</v>
+        <v>0.334351</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.974</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.8305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1016/j.cej.2024.149370 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1016/j.cej.2024.149370</t>
+          <t>10.1016/j.cattod.2020.05.049</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.994806</v>
+        <v>0.0138623</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.9235</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.988</v>
+        <v>0.8115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1016/j.mcat.2020.111105 | 30 bar | H2/CO2 3 | 10000 h-1</t>
+          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.1016/j.mcat.2020.111105</t>
+          <t>10.1021/acs.iecr.7b01464</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.975586</v>
+        <v>0.013812</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.996</v>
+        <v>0.9535</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9645</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.953</v>
+        <v>0.8285</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.849194</v>
+        <v>0.116837</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.992</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.881</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
+          <t>10.1021/acscatal.5c05984</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.831378</v>
+        <v>0.0175227</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.954</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.99</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1002/ente.201800747 | 40 bar | H2/CO2 3 | 21.6 NL/g/h</t>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.1002/ente.201800747</t>
+          <t>10.1039/c6ra28305e</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.829407</v>
+        <v>0.012303</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.802</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6065</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.993</v>
+        <v>0.5085</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290</t>
+          <t>10.1021/acscatal.9b03305</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5083259999999999</v>
+        <v>0.00625936</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.6695</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.7065</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.964</v>
+        <v>0.7725</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24000 h-1</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.128376</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.501371</v>
+        <v>0.000191829</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0.5125</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.5135</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9805</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.9245</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290 | 20 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.1701290</t>
+          <t>10.1016/j.fuel.2024.131111</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.477993</v>
+        <v>0.00163138</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0.389</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.2325</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.988</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2023.128376 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2023.128376</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.380904</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 4 | 24000 h-1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.9b01869</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.364283</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>10.1021/acsaem.1c01502 | 50 bar | H2/CO2 3 | 30 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>10.1021/acsaem.1c01502</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.352455</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.9845</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.aaz2060</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.335596</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.8695000000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcata.2018.04.036 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcata.2018.04.036</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.279156</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9145</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.9055</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>10.1016/j.jes.2023.05.010</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.26376</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.1701290 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.1701290</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.259628</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.974</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>10.1038/s41467-021-22224-x | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>10.1038/s41467-021-22224-x</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.217273</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.9025</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.176094</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.8055</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.8215</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcat.2016.03.017 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcat.2016.03.017</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.159201</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.9b03305</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.144612</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10.1021/acs.iecr.7b01464</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.136346</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.9665</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.955</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.abi6012</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0.133089</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>10.1021/cs500979c | 80 bar | H2/CO2 3 | 3600 h-1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10.1021/cs500979c</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>0.095912</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.9985000000000001</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.9225</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>10.1126/sciadv.abi6012</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0932558</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.9955000000000001</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.909</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>10.1039/c6ra28305e</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.0264893</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.8445</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c05628 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c05628</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.666845</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.8745000000000001</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.1c03170 | 30 bar | H2/CO2 3 | 60 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.1c03170</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0.627734</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.9895</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.9795</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>10.1002/anie.202401168 | 30 bar | H2/CO2 3 | 9 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10.1002/anie.202401168</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0.528884</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.9995000000000001</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.9855</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.921</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2020.05.049</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0.549488</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.216698</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.9415</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.8975</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.9965000000000001</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5b00682 | 30 bar | H2/CO2 4 | 16 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5b00682</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3.72737</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.9965000000000001</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.9485</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.887</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>2.9939</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.9065</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.9935</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.5c05984</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0.0817657</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcou.2022.102209 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcou.2022.102209</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1.00804</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.926</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 18 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0.01152</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.8015</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.5655</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.526</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>10.1016/j.jcat.2012.05.020</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>0.376425</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0.9765</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.6805</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.9715</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcatb.2017.06.069 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>10.1016/j.apcatb.2017.06.069</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0.448368</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0.9705</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.8875</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.7805</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.864</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.12945</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.9435</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.7375</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.947</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>10.1021/acsami.1c05586 | 30 bar | H2/CO2 3 | 7.2 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>10.1021/acsami.1c05586</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>2.0512</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.9405</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.6145</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2019.05.040 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>10.1016/j.cattod.2019.05.040</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.275299</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.9285</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.7875</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.916</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2023.127927</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0274762</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.7385</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.8535</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>10.1039/c5ra04774a | 30 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>10.1039/c5ra04774a</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.08487260000000001</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.8075</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.8035</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.8685</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324 | 30 bar | H2/CO2 3 | 6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.158936</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.6545</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.5955</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.476</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>10.1002/cctc.202000974</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.00633792</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.7035</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.6445</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324 | 30 bar | H2/CO2 3 | 14 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>10.1021/acscatal.0c03324</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0449574</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.5145</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.513</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>0.0202078</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0.5405</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.5365</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111 | 60 bar | H2/CO2 10 | 116 NL/g/h</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10.1016/j.fuel.2024.131111</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.00393752</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0.5315</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.5004999999999999</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 4000 h-1</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>0.000856731</v>
-      </c>
-      <c r="D57" t="n">
-        <v>0.4815</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.489</v>
+        <v>0.1245</v>
       </c>
     </row>
   </sheetData>
@@ -3333,22 +2197,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6835443037974683</v>
+        <v>0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3619631901840491</v>
+        <v>0.4406779661016949</v>
       </c>
     </row>
     <row r="5">
@@ -3361,22 +2225,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6582278481012658</v>
+        <v>0.65</v>
       </c>
       <c r="F5" t="n">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.4193548387096774</v>
       </c>
     </row>
     <row r="6">
@@ -3389,22 +2253,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
         <v>0.675</v>
       </c>
       <c r="F6" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3705882352941177</v>
+        <v>0.4516129032258064</v>
       </c>
     </row>
     <row r="7">
@@ -3417,22 +2281,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.4677419354838709</v>
       </c>
     </row>
     <row r="8">
@@ -3445,22 +2309,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6506024096385542</v>
+        <v>0.675</v>
       </c>
       <c r="F8" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3470588235294118</v>
+        <v>0.4516129032258064</v>
       </c>
     </row>
     <row r="9">
@@ -3473,22 +2337,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5783132530120482</v>
+        <v>0.6</v>
       </c>
       <c r="F9" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3176470588235294</v>
+        <v>0.4193548387096774</v>
       </c>
     </row>
     <row r="10">
@@ -3501,22 +2365,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5542168674698795</v>
+        <v>0.6</v>
       </c>
       <c r="F10" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G10" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.4516129032258064</v>
       </c>
     </row>
     <row r="11">
@@ -3529,22 +2393,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4698795180722892</v>
+        <v>0.45</v>
       </c>
       <c r="F11" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2823529411764706</v>
+        <v>0.4032258064516129</v>
       </c>
     </row>
     <row r="12">
@@ -3557,22 +2421,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4939759036144578</v>
+        <v>0.475</v>
       </c>
       <c r="F12" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2411764705882353</v>
+        <v>0.4032258064516129</v>
       </c>
     </row>
     <row r="13">
@@ -3585,22 +2449,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4698795180722892</v>
+        <v>0.425</v>
       </c>
       <c r="F13" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2235294117647059</v>
+        <v>0.3709677419354839</v>
       </c>
     </row>
     <row r="14">
@@ -3613,22 +2477,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4457831325301205</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2117647058823529</v>
+        <v>0.3548387096774194</v>
       </c>
     </row>
     <row r="15">
@@ -3637,26 +2501,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none (primary)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4216867469879518</v>
+        <v>0.375</v>
       </c>
       <c r="F15" t="n">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.3387096774193548</v>
       </c>
     </row>
     <row r="18">

--- a/source_data/SourceData_EDFig3.xlsx
+++ b/source_data/SourceData_EDFig3.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of analysis/meoh_main_result_stats_2026_10_06/summary.json; 95 % CI checked against summary.json</t>
+          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv and analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of each summary.json; 95 % CIs checked against summary.json</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv</t>
+          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/regret_threshold_curve.csv</t>
+          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/regret_threshold_curve.csv, analysis/meoh_main_result_stats_2026_10_06/regret_threshold_curve.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/summary.json (noise.*)</t>
+          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json, analysis/meoh_main_result_stats_2026_10_06/summary.json (noise.*)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/summary.json</t>
+          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json,</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch == True)</t>
+          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv, analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch == True); near-infeasible: analysis/meoh_s6_robustness_2026_10_13/s6_groups.csv (cls)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -588,28 +588,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (limit_sweep, isothermal); published reactor-inlet compositions in analysis/meoh_literature_inversion_2026_10_05/inlet_inert_literature.csv</t>
+          <t>see column source</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>constants drawn on panel e</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -622,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -666,7 +648,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of analysis/meoh_main_result_stats_2026_10_06/summary.json; 95 % CI checked against summary.json</t>
+          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv and analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of each summary.json; 95 % CIs checked against summary.json</t>
         </is>
       </c>
     </row>
@@ -683,7 +665,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>resamples</t>
+          <t>resamples_inlet_limited</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>resamples_no_limit</t>
         </is>
       </c>
     </row>
@@ -695,6 +682,9 @@
         <v>0.02</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -706,6 +696,9 @@
         <v>0.04</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -719,6 +712,9 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -728,6 +724,9 @@
         <v>0.08</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
         <v>13</v>
       </c>
     </row>
@@ -739,6 +738,9 @@
         <v>0.1</v>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>30</v>
       </c>
     </row>
@@ -750,6 +752,9 @@
         <v>0.12</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>34</v>
       </c>
     </row>
@@ -761,6 +766,9 @@
         <v>0.14</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
         <v>96</v>
       </c>
     </row>
@@ -772,6 +780,9 @@
         <v>0.16</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>135</v>
       </c>
     </row>
@@ -783,6 +794,9 @@
         <v>0.18</v>
       </c>
       <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
         <v>235</v>
       </c>
     </row>
@@ -794,6 +808,9 @@
         <v>0.2</v>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
         <v>261</v>
       </c>
     </row>
@@ -805,6 +822,9 @@
         <v>0.22</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
         <v>443</v>
       </c>
     </row>
@@ -816,6 +836,9 @@
         <v>0.24</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>397</v>
       </c>
     </row>
@@ -827,6 +850,9 @@
         <v>0.26</v>
       </c>
       <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
         <v>489</v>
       </c>
     </row>
@@ -838,6 +864,9 @@
         <v>0.28</v>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>444</v>
       </c>
     </row>
@@ -849,6 +878,9 @@
         <v>0.3</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>481</v>
       </c>
     </row>
@@ -860,6 +892,9 @@
         <v>0.32</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
         <v>637</v>
       </c>
     </row>
@@ -871,6 +906,9 @@
         <v>0.34</v>
       </c>
       <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
         <v>575</v>
       </c>
     </row>
@@ -882,6 +920,9 @@
         <v>0.36</v>
       </c>
       <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
         <v>740</v>
       </c>
     </row>
@@ -893,6 +934,9 @@
         <v>0.38</v>
       </c>
       <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
         <v>638</v>
       </c>
     </row>
@@ -904,6 +948,9 @@
         <v>0.4</v>
       </c>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
         <v>552</v>
       </c>
     </row>
@@ -915,6 +962,9 @@
         <v>0.42</v>
       </c>
       <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
         <v>683</v>
       </c>
     </row>
@@ -926,6 +976,9 @@
         <v>0.44</v>
       </c>
       <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>609</v>
       </c>
     </row>
@@ -937,6 +990,9 @@
         <v>0.46</v>
       </c>
       <c r="C26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" t="n">
         <v>551</v>
       </c>
     </row>
@@ -948,6 +1004,9 @@
         <v>0.48</v>
       </c>
       <c r="C27" t="n">
+        <v>23</v>
+      </c>
+      <c r="D27" t="n">
         <v>445</v>
       </c>
     </row>
@@ -959,6 +1018,9 @@
         <v>0.5</v>
       </c>
       <c r="C28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D28" t="n">
         <v>238</v>
       </c>
     </row>
@@ -970,6 +1032,9 @@
         <v>0.52</v>
       </c>
       <c r="C29" t="n">
+        <v>79</v>
+      </c>
+      <c r="D29" t="n">
         <v>411</v>
       </c>
     </row>
@@ -981,6 +1046,9 @@
         <v>0.54</v>
       </c>
       <c r="C30" t="n">
+        <v>107</v>
+      </c>
+      <c r="D30" t="n">
         <v>305</v>
       </c>
     </row>
@@ -992,6 +1060,9 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C31" t="n">
+        <v>184</v>
+      </c>
+      <c r="D31" t="n">
         <v>211</v>
       </c>
     </row>
@@ -1003,6 +1074,9 @@
         <v>0.58</v>
       </c>
       <c r="C32" t="n">
+        <v>239</v>
+      </c>
+      <c r="D32" t="n">
         <v>136</v>
       </c>
     </row>
@@ -1014,6 +1088,9 @@
         <v>0.6</v>
       </c>
       <c r="C33" t="n">
+        <v>343</v>
+      </c>
+      <c r="D33" t="n">
         <v>93</v>
       </c>
     </row>
@@ -1025,6 +1102,9 @@
         <v>0.62</v>
       </c>
       <c r="C34" t="n">
+        <v>567</v>
+      </c>
+      <c r="D34" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1036,6 +1116,9 @@
         <v>0.64</v>
       </c>
       <c r="C35" t="n">
+        <v>702</v>
+      </c>
+      <c r="D35" t="n">
         <v>35</v>
       </c>
     </row>
@@ -1047,6 +1130,9 @@
         <v>0.66</v>
       </c>
       <c r="C36" t="n">
+        <v>878</v>
+      </c>
+      <c r="D36" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1058,6 +1144,9 @@
         <v>0.68</v>
       </c>
       <c r="C37" t="n">
+        <v>853</v>
+      </c>
+      <c r="D37" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1069,6 +1158,9 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="C38" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D38" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1080,6 +1172,9 @@
         <v>0.72</v>
       </c>
       <c r="C39" t="n">
+        <v>970</v>
+      </c>
+      <c r="D39" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1091,6 +1186,9 @@
         <v>0.74</v>
       </c>
       <c r="C40" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1102,6 +1200,9 @@
         <v>0.76</v>
       </c>
       <c r="C41" t="n">
+        <v>898</v>
+      </c>
+      <c r="D41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1113,6 +1214,9 @@
         <v>0.78</v>
       </c>
       <c r="C42" t="n">
+        <v>701</v>
+      </c>
+      <c r="D42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1124,75 +1228,294 @@
         <v>0.8</v>
       </c>
       <c r="C43" t="n">
+        <v>513</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>421</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C45" t="n">
+        <v>179</v>
+      </c>
+      <c r="D45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="C46" t="n">
+        <v>75</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C47" t="n">
+        <v>52</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>constants drawn on panel a</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>point</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>papers</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>inlet_limited.name</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>inert-limited loop</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>inlet_limited.point</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>inlet_limited.mismatched</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>inlet_limited.ci</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0.540541, 0.827586</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>no_limit.name</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>no limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>no_limit.point</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
         <v>0.375</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ci</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>no_limit.mismatched</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>no_limit.ci</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>0.151515, 0.571429</t>
         </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>groups</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1206,7 +1529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1250,7 +1573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/regret_threshold_curve.csv</t>
+          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/regret_threshold_curve.csv, analysis/meoh_main_result_stats_2026_10_06/regret_threshold_curve.csv</t>
         </is>
       </c>
     </row>
@@ -1262,17 +1585,22 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>groups</t>
+          <t>groups_inlet_limited</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>papers_inlet_limited</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>papers</t>
+          <t>groups_no_limit</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>papers_no_limit</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1609,15 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C4" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" t="n">
         <v>15</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1295,12 +1626,15 @@
         <v>0.001</v>
       </c>
       <c r="B5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n">
         <v>14</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1309,12 +1643,15 @@
         <v>0.005</v>
       </c>
       <c r="B6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="n">
         <v>13</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1323,12 +1660,15 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" t="n">
         <v>12</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1337,12 +1677,15 @@
         <v>0.02</v>
       </c>
       <c r="B8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n">
         <v>8</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1351,12 +1694,15 @@
         <v>0.05</v>
       </c>
       <c r="B9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1365,12 +1711,15 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1385,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1429,52 +1778,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/summary.json (noise.*)</t>
+          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json, analysis/meoh_main_result_stats_2026_10_06/summary.json (noise.*)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>loop</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>observed</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>mismatch_groups_mean</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>mismatch_groups_q025</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>mismatch_groups_q975</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>noise_floor_mean</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>noise_floor_q025</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>noise_floor_q975</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>robust_ge90pct</t>
         </is>
@@ -1483,155 +1842,292 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>meas_k1</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>re-measured, error x1</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>16.486</v>
-      </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>27.813</v>
       </c>
       <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="n">
         <v>4.208</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="n">
-        <v>11</v>
+      <c r="K4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>meas_k2</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>re-measured, error x2</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>17.394</v>
-      </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>27.4895</v>
       </c>
       <c r="F5" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" t="n">
         <v>8.000999999999999</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
-        <v>9</v>
+      <c r="K5" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>meas_k4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>re-measured, error x4</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>26.999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>23</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13.7155</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>meas_k1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>re-measured, error x1</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.486</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.208</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>meas_k2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>re-measured, error x2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>17.394</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.000999999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>meas_k4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>re-measured, error x4</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
         <v>17.988</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F9" t="n">
         <v>13</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G9" t="n">
         <v>22</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H9" t="n">
         <v>13.7175</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I9" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J9" t="n">
         <v>19</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K9" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>constants drawn on panel c</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/summary.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>observed</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>draws</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B15" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>groups</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1646,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1690,400 +2186,1426 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch == True)</t>
+          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv, analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch == True); near-infeasible: analysis/meoh_s6_robustness_2026_10_13/s6_groups.csv (cls)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>loop</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>doi</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>observed_regret</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>p_mismatch_meas_k1</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>p_mismatch_meas_k2</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>p_mismatch_meas_k4</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>near_infeasible</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>10.1039/c2cy20604h</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.828627</v>
-      </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.57562</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.973</v>
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.57546</v>
+          <t>10.1039/d0gc01597k | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.1039/d0gc01597k</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0.982642</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.167776</v>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aaz2060</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.831378</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.982</v>
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.115626</v>
+          <t>10.1002/ente.201800747 | 40 bar | H2/CO2 3 | 21.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10.1002/ente.201800747</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0.7963479999999999</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9605</v>
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0501492</v>
+          <t>10.1016/j.fuel.2022.125878 | 30 bar | H2/CO2 3 | 12000 h-1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2022.125878</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.612582</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9985000000000001</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9825</v>
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0354367</v>
+          <t>10.1021/acscatal.0c05628 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.0c05628</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.531343</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9885</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.843</v>
+        <v>0.957</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.334351</v>
+          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 4 | 24000 h-1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b01869</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.364283</v>
       </c>
       <c r="E10" t="n">
-        <v>0.974</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8305</v>
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0138623</v>
+          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10.1016/j.jes.2023.05.010</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.23079</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9235</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8115</v>
+        <v>0.997</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9415</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.013812</v>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.144612</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9535</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8285</v>
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.116837</v>
+          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01464</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.992</v>
+        <v>0.136346</v>
       </c>
       <c r="E13" t="n">
-        <v>0.881</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.737</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.0175227</v>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.954</v>
+        <v>0.133089</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8735000000000001</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.796</v>
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.012303</v>
+          <t>10.1021/cs500979c | 80 bar | H2/CO2 3 | 3600 h-1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.1021/cs500979c</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>0.802</v>
+        <v>0.095912</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6065</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5085</v>
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.00625936</v>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>0.6695</v>
+        <v>0.0365433</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7065</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7725</v>
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.000191829</v>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>0.5125</v>
+        <v>0.0264893</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5135</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.473</v>
+        <v>0.9815</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.08781</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9775</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.549488</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9655</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9085</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>10.1016/j.fuel.2024.131111</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D20" t="n">
+        <v>0.118529</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9285</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.216698</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0817657</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8465</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.9939</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9935</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2012.05.020</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.376425</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9705</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6755</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2018.04.036 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10.1016/j.apcata.2018.04.036</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.785093</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.1c03170 | 30 bar | H2/CO2 3 | 60 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.1c03170</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.628244</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9425</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.6395</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.12945</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.00633792</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6415</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0202078</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.7135</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.00293911</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.000856731</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.828627</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.57546</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.167776</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aaz2060</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.115626</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0501492</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0354367</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9885</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.334351</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0138623</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9235</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01464</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.013812</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9535</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.8285</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.116837</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0175227</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.8735000000000001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.012303</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.5085</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.00625936</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.6695</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.7065</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.7725</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.000191829</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.5135</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>0.00163138</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E46" t="n">
         <v>0.389</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F46" t="n">
         <v>0.2325</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G46" t="n">
         <v>0.1245</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2097,7 +3619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2141,14 +3663,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json (limit_sweep, isothermal); published reactor-inlet compositions in analysis/meoh_literature_inversion_2026_10_05/inlet_inert_literature.csv</t>
+          <t>source: see column source</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>limit</t>
+          <t>check</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
@@ -2158,416 +3680,755 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>loop</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
           <t>groups</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>mismatched</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>share</t>
-        </is>
-      </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>iso_groups</t>
+          <t>disagreements</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>iso_mismatched</t>
+          <t>regret_gt5pct</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>iso_share</t>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>0.04</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>as published</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>as published</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>40</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>28</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.7</v>
       </c>
-      <c r="F4" t="n">
-        <v>59</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.primary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>as published</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>as published</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.primary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>without the study with most comparisons</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>without the study
+with most comparisons</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>without_bansode</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.without_bansode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>without the study with most comparisons</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>without the study
+with most comparisons</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>without_bansode</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.without_bansode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>plot-read entries added</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>plot-read entries
+added</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>all_entries</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>82</v>
+      </c>
+      <c r="F8" t="n">
+        <v>54</v>
+      </c>
+      <c r="G8" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6585365853658537</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.all_entries_inlet_limit / all_entries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>plot-read entries added</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>plot-read entries
+added</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>all_entries</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4216867469879518</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.all_entries_inlet_limit / all_entries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>products close to MeOH, CO, CH4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>products close to
+MeOH, CO, CH$_4$</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>closure_ge95</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>28</v>
+      </c>
+      <c r="F10" t="n">
+        <v>17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.closure_ge95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>products close to MeOH, CO, CH4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>products close to
+MeOH, CO, CH$_4$</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>closure_ge95</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>28</v>
+      </c>
+      <c r="F11" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.3928571428571428</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.closure_ge95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>unreported split: all CO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>unreported split:
+all CO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>split_all_CO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
         <v>26</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.4406779661016949</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unreported split: all CO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>unreported split:
+all CO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>split_all_CO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>40</v>
       </c>
-      <c r="D5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F5" t="n">
-        <v>62</v>
-      </c>
-      <c r="G5" t="n">
-        <v>26</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="F13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.low)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>unreported split: all CH4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>unreported split:
+all CH$_4$</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>split_all_CH4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>40</v>
       </c>
-      <c r="D6" t="n">
-        <v>27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="F6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F14" t="n">
+        <v>29</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.high)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unreported split: all CH4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>unreported split:
+all CH$_4$</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>split_all_CH4</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.high)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>recycled CO as inert</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>recycled CO
+as inert</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>inert_co</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>40</v>
+      </c>
+      <c r="F16" t="n">
         <v>28</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.4516129032258064</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.06862515529373837</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>reference loop 6.86%</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="G16" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.inert_co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>recycled CO as inert</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>recycled CO
+as inert</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>inert_co</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>40</v>
       </c>
-      <c r="D7" t="n">
-        <v>28</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F7" t="n">
-        <v>62</v>
-      </c>
-      <c r="G7" t="n">
-        <v>29</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.4677419354838709</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="F17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" t="n">
+        <v>13</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.inert_co)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>catalyst priced from composition</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>catalyst priced
+from composition</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>catalyst_priced</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>40</v>
       </c>
-      <c r="D8" t="n">
-        <v>27</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="F8" t="n">
-        <v>62</v>
-      </c>
-      <c r="G8" t="n">
-        <v>28</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.4516129032258064</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>40</v>
-      </c>
-      <c r="D9" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>62</v>
-      </c>
-      <c r="G9" t="n">
-        <v>26</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>40</v>
-      </c>
-      <c r="D10" t="n">
-        <v>24</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>62</v>
-      </c>
-      <c r="G10" t="n">
-        <v>28</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.4516129032258064</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>40</v>
-      </c>
-      <c r="D11" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F11" t="n">
-        <v>62</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="F18" t="n">
         <v>25</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.4032258064516129</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>40</v>
-      </c>
-      <c r="D12" t="n">
-        <v>19</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="F12" t="n">
-        <v>62</v>
-      </c>
-      <c r="G12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4032258064516129</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>40</v>
-      </c>
-      <c r="D13" t="n">
-        <v>17</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="F13" t="n">
-        <v>62</v>
-      </c>
-      <c r="G13" t="n">
-        <v>23</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3709677419354839</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>40</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F14" t="n">
-        <v>62</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="G18" t="n">
         <v>22</v>
       </c>
-      <c r="H14" t="n">
-        <v>0.3548387096774194</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v/>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>none (primary)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>40</v>
-      </c>
-      <c r="D15" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="F15" t="n">
-        <v>62</v>
-      </c>
-      <c r="G15" t="n">
-        <v>21</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.3387096774193548</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>constants drawn on panel e</t>
+      <c r="H18" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (catalyst_cost.S6/S5.variants.composition_3y)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_literature_inversion_2026_10_05/summary.json</t>
+          <t>catalyst priced from composition</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>catalyst priced
+from composition</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>catalyst_priced</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>40</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (catalyst_cost.S6/S5.variants.composition_3y)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>more catalyst, conversion raised</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>more catalyst,
+conversion raised</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>conversion_raised</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" t="n">
+        <v>23</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>analysis/verify_2026_10_12_s6_conversion/s6_conversion_summary.json / analysis/meoh_literature_inversion_2026_10_05/conversion_sensitivity_summary.json (printed|cost_f0.95)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>reference</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.06862515529373837</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>literature</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.0492, 0.10249, 4</t>
+          <t>more catalyst, conversion raised</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>more catalyst,
+conversion raised</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>conversion_raised</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>40</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>analysis/verify_2026_10_12_s6_conversion/s6_conversion_summary.json / analysis/meoh_literature_inversion_2026_10_05/conversion_sensitivity_summary.json (printed|cost_f0.95)</t>
         </is>
       </c>
     </row>

--- a/source_data/SourceData_EDFig3.xlsx
+++ b/source_data/SourceData_EDFig3.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv and analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of each summary.json; 95 % CIs checked against summary.json</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/group_noise_probabilities.csv and analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of each summary.json; 95 % CIs checked against summary.json</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/group_noise_probabilities.csv</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -516,7 +516,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/regret_threshold_curve.csv, analysis/meoh_main_result_stats_2026_10_06/regret_threshold_curve.csv</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/regret_threshold_curve.csv, analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/regret_threshold_curve.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -534,7 +534,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json, analysis/meoh_main_result_stats_2026_10_06/summary.json (noise.*)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/summary.json, analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/summary.json (noise.*)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json,</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/summary.json,</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv, analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch == True); near-infeasible: analysis/meoh_s6_robustness_2026_10_13/s6_groups.csv (cls)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/group_noise_probabilities.csv, analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/group_noise_probabilities.csv (observed_mismatch == True); near-infeasible: PR #69 rule on analysis/meoh_field_pooled_2026_10_15/pooled_candidates.csv</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -648,7 +648,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv and analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of each summary.json; 95 % CIs checked against summary.json</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/group_noise_probabilities.csv and analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/group_noise_probabilities.csv (observed_mismatch, doi) re-drawn with the seed and resample count of each summary.json; 95 % CIs checked against summary.json</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -741,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -755,7 +755,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>96</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
@@ -797,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>235</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>261</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>443</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15">
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>397</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16">
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>489</v>
+        <v>821</v>
       </c>
     </row>
     <row r="17">
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>444</v>
+        <v>989</v>
       </c>
     </row>
     <row r="18">
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>481</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="19">
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>637</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="20">
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>575</v>
+        <v>978</v>
       </c>
     </row>
     <row r="21">
@@ -920,10 +920,10 @@
         <v>0.36</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>740</v>
+        <v>900</v>
       </c>
     </row>
     <row r="22">
@@ -934,10 +934,10 @@
         <v>0.38</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>638</v>
+        <v>713</v>
       </c>
     </row>
     <row r="23">
@@ -948,10 +948,10 @@
         <v>0.4</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>552</v>
+        <v>495</v>
       </c>
     </row>
     <row r="24">
@@ -962,10 +962,10 @@
         <v>0.42</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>683</v>
+        <v>383</v>
       </c>
     </row>
     <row r="25">
@@ -976,10 +976,10 @@
         <v>0.44</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D25" t="n">
-        <v>609</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26">
@@ -990,10 +990,10 @@
         <v>0.46</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D26" t="n">
-        <v>551</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27">
@@ -1004,10 +1004,10 @@
         <v>0.48</v>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="D27" t="n">
-        <v>445</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
@@ -1018,10 +1018,10 @@
         <v>0.5</v>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="D28" t="n">
-        <v>238</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
@@ -1032,10 +1032,10 @@
         <v>0.52</v>
       </c>
       <c r="C29" t="n">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="D29" t="n">
-        <v>411</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -1046,10 +1046,10 @@
         <v>0.54</v>
       </c>
       <c r="C30" t="n">
-        <v>107</v>
+        <v>461</v>
       </c>
       <c r="D30" t="n">
-        <v>305</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1060,10 +1060,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>184</v>
+        <v>688</v>
       </c>
       <c r="D31" t="n">
-        <v>211</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1074,10 +1074,10 @@
         <v>0.58</v>
       </c>
       <c r="C32" t="n">
-        <v>239</v>
+        <v>949</v>
       </c>
       <c r="D32" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1088,10 +1088,10 @@
         <v>0.6</v>
       </c>
       <c r="C33" t="n">
-        <v>343</v>
+        <v>1112</v>
       </c>
       <c r="D33" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1102,10 +1102,10 @@
         <v>0.62</v>
       </c>
       <c r="C34" t="n">
-        <v>567</v>
+        <v>1363</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1116,10 +1116,10 @@
         <v>0.64</v>
       </c>
       <c r="C35" t="n">
-        <v>702</v>
+        <v>1344</v>
       </c>
       <c r="D35" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1130,10 +1130,10 @@
         <v>0.66</v>
       </c>
       <c r="C36" t="n">
-        <v>878</v>
+        <v>1218</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1144,10 +1144,10 @@
         <v>0.68</v>
       </c>
       <c r="C37" t="n">
-        <v>853</v>
+        <v>924</v>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1158,10 +1158,10 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>1133</v>
+        <v>689</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1172,10 +1172,10 @@
         <v>0.72</v>
       </c>
       <c r="C39" t="n">
-        <v>970</v>
+        <v>338</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1186,7 +1186,7 @@
         <v>0.74</v>
       </c>
       <c r="C40" t="n">
-        <v>1024</v>
+        <v>191</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0.76</v>
       </c>
       <c r="C41" t="n">
-        <v>898</v>
+        <v>64</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
         <v>0.78</v>
       </c>
       <c r="C42" t="n">
-        <v>701</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="C43" t="n">
-        <v>513</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>421</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0.84</v>
       </c>
       <c r="C45" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0.86</v>
       </c>
       <c r="C46" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         <v>0.88</v>
       </c>
       <c r="C47" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
         <v>0.9</v>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>0.92</v>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/group_noise_probabilities.csv</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7</v>
+        <v>0.6172839506172839</v>
       </c>
     </row>
     <row r="64">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0.540541, 0.827586</t>
+          <t>0.488869, 0.722222</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.375</v>
+        <v>0.308641975308642</v>
       </c>
     </row>
     <row r="68">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0.151515, 0.571429</t>
+          <t>0.16901, 0.445962</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/regret_threshold_curve.csv, analysis/meoh_main_result_stats_2026_10_06/regret_threshold_curve.csv</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/regret_threshold_curve.csv, analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/regret_threshold_curve.csv</t>
         </is>
       </c>
     </row>
@@ -1609,16 +1609,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" t="n">
         <v>15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1626,16 +1626,16 @@
         <v>0.001</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" t="n">
         <v>14</v>
-      </c>
-      <c r="E5" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1643,16 +1643,16 @@
         <v>0.005</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E6" t="n">
         <v>13</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -1660,16 +1660,16 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" t="n">
         <v>19</v>
       </c>
-      <c r="D7" t="n">
-        <v>12</v>
-      </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1677,16 +1677,16 @@
         <v>0.02</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1694,16 +1694,16 @@
         <v>0.05</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1711,16 +1711,16 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1778,7 +1778,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json, analysis/meoh_main_result_stats_2026_10_06/summary.json (noise.*)</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/summary.json, analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/summary.json (noise.*)</t>
         </is>
       </c>
     </row>
@@ -1856,28 +1856,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>27.813</v>
+        <v>49.904</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H4" t="n">
-        <v>4.208</v>
+        <v>9.0725</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>27.4895</v>
+        <v>49.878</v>
       </c>
       <c r="F5" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H5" t="n">
-        <v>8.000999999999999</v>
+        <v>16.6455</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -1938,28 +1938,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>26.999</v>
+        <v>49.735</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H6" t="n">
-        <v>13.7155</v>
+        <v>27.45</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -1979,28 +1979,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>16.486</v>
+        <v>28.685</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>4.208</v>
+        <v>9.0725</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -2020,28 +2020,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>17.394</v>
+        <v>30.5415</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H8" t="n">
-        <v>8.000999999999999</v>
+        <v>16.6455</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J8" t="n">
+        <v>23</v>
+      </c>
+      <c r="K8" t="n">
         <v>12</v>
-      </c>
-      <c r="K8" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2061,28 +2061,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>17.988</v>
+        <v>32.926</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H9" t="n">
-        <v>13.7175</v>
+        <v>27.451</v>
       </c>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2095,7 +2095,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/summary.json,</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/summary.json,</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2142,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2186,7 +2186,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_s6_robustness_2026_10_13/stats_s6/group_noise_probabilities.csv, analysis/meoh_main_result_stats_2026_10_06/group_noise_probabilities.csv (observed_mismatch == True); near-infeasible: analysis/meoh_s6_robustness_2026_10_13/s6_groups.csv (cls)</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/stats_s6/group_noise_probabilities.csv, analysis/meoh_field_pooled_2026_10_15/robustness/stats_s5/group_noise_probabilities.csv (observed_mismatch == True); near-infeasible: PR #69 rule on analysis/meoh_field_pooled_2026_10_15/pooled_candidates.csv</t>
         </is>
       </c>
     </row>
@@ -2240,16 +2240,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1021/acscatal.6c02907 | 10 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.57562</v>
+        <v>3.57216</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.995</v>
+        <v>0.9935</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -2272,25 +2272,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.1039/d0gc01597k | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10.1039/d0gc01597k</t>
+          <t>10.1021/acscatal.6c03987</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.982642</v>
+        <v>1.7752</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -2304,16 +2304,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.831378</v>
+        <v>1.57562</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -2322,10 +2322,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9925</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2336,16 +2336,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.1002/ente.201800747 | 40 bar | H2/CO2 3 | 21.6 NL/g/h</t>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10.1002/ente.201800747</t>
+          <t>10.1126/sciadv.aea7041</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7963479999999999</v>
+        <v>1.45557</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -2368,16 +2368,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2022.125878 | 30 bar | H2/CO2 3 | 12000 h-1</t>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2022.125878</t>
+          <t>10.1021/acscatal.6c03987</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.612582</v>
+        <v>1.40149</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -2400,25 +2400,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.0c05628 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.0c05628</t>
+          <t>10.1021/acscatal.6c06714</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.531343</v>
+        <v>1.3414</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.957</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -2432,25 +2432,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 4 | 24000 h-1</t>
+          <t>10.1021/acscatal.6c02907 | 2.5 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b01869</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.364283</v>
+        <v>1.19155</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
       <c r="G10" t="n">
-        <v>0.998</v>
+        <v>0.9065</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10.1016/j.jes.2023.05.010</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.23079</v>
+        <v>1.13975</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9415</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -2496,28 +2496,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.144612</v>
+        <v>1.08781</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9775</v>
       </c>
       <c r="G12" t="n">
-        <v>0.984</v>
+        <v>0.872</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2528,28 +2528,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.136346</v>
+        <v>1.06857</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9805</v>
+        <v>0.9735</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2560,28 +2560,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+          <t>10.1039/d0gc01597k | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1039/d0gc01597k</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.133089</v>
+        <v>0.982642</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.999</v>
+        <v>0.9485</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2592,16 +2592,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.1021/cs500979c | 80 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10.1021/cs500979c</t>
+          <t>10.1126/sciadv.aaz2060</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.095912</v>
+        <v>0.831378</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -2610,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.921</v>
+        <v>1</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
@@ -2624,28 +2624,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+          <t>10.1021/acs.iecr.6c02654 | 30 bar | H2/CO2 3 | 18 NL/g/h</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1021/acs.iecr.6c02654</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.0365433</v>
+        <v>0.820562</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="G16" t="n">
-        <v>0.979</v>
+        <v>0.8925</v>
       </c>
       <c r="H16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -2656,25 +2656,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>10.1002/ente.201800747 | 40 bar | H2/CO2 3 | 21.6 NL/g/h</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e</t>
+          <t>10.1002/ente.201800747</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.0264893</v>
+        <v>0.7963479999999999</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9815</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.831</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -2688,25 +2688,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 120 NL/g/h</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.08781</v>
+        <v>0.720702</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9775</v>
+        <v>0.997</v>
       </c>
       <c r="G18" t="n">
-        <v>0.879</v>
+        <v>0.974</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -2720,28 +2720,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1016/j.fuel.2022.125878 | 30 bar | H2/CO2 3 | 12000 h-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049</t>
+          <t>10.1016/j.fuel.2022.125878</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.549488</v>
+        <v>0.612582</v>
       </c>
       <c r="E19" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9655</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9085</v>
+        <v>1</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2752,28 +2752,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 4 | 24000 h-1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2024.131111</t>
+          <t>10.1021/acscatal.9b01869</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.118529</v>
+        <v>0.364283</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9975000000000001</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9285</v>
+        <v>1</v>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2784,28 +2784,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 2 | 48 NL/g/h</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acscatal.6c04842</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.216698</v>
+        <v>0.364174</v>
       </c>
       <c r="E21" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.887</v>
+        <v>0.8865</v>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2816,25 +2816,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+          <t>10.1021/acscatal.6c02907 | 40 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.0817657</v>
+        <v>0.317472</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9965000000000001</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8465</v>
+        <v>0.9655</v>
       </c>
       <c r="H22" t="b">
         <v>0</v>
@@ -2848,25 +2848,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1016/j.jes.2023.05.010</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.9939</v>
+        <v>0.23079</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9935</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9115</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.798</v>
+        <v>0.928</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -2880,28 +2880,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.1016/j.jcat.2012.05.020</t>
+          <t>10.1021/acscatal.6c04842</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.376425</v>
+        <v>0.178319</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9705</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0.822</v>
+        <v>0.9585</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6755</v>
+        <v>0.78</v>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2912,25 +2912,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2018.04.036 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10.1016/j.apcata.2018.04.036</t>
+          <t>10.1021/acscatal.9b03305</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.785093</v>
+        <v>0.144612</v>
       </c>
       <c r="E25" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.82</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.643</v>
+        <v>0.9845</v>
       </c>
       <c r="H25" t="b">
         <v>0</v>
@@ -2944,28 +2944,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.1c03170 | 30 bar | H2/CO2 3 | 60 NL/g/h</t>
+          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.1c03170</t>
+          <t>10.1021/acs.iecr.7b01464</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.628244</v>
+        <v>0.136346</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9425</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.782</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6395</v>
+        <v>0.977</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2976,25 +2976,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.12945</v>
+        <v>0.133089</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9385</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.836</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.718</v>
+        <v>1</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
@@ -3008,25 +3008,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1021/cs500979c | 80 bar | H2/CO2 3 | 3600 h-1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10.1002/cctc.202000974</t>
+          <t>10.1021/cs500979c</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.00633792</v>
+        <v>0.095912</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6415</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.928</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
@@ -3040,25 +3040,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1126/sciadv.abi6012</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.0202078</v>
+        <v>0.0365433</v>
       </c>
       <c r="E29" t="n">
-        <v>0.537</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7135</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.844</v>
+        <v>0.9725</v>
       </c>
       <c r="H29" t="b">
         <v>0</v>
@@ -3072,28 +3072,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10.1016/j.fuel.2023.127927</t>
+          <t>10.1039/c6ra28305e</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.00293911</v>
+        <v>0.0264893</v>
       </c>
       <c r="E30" t="n">
-        <v>0.537</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5075</v>
+        <v>0.977</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5495</v>
+        <v>0.844</v>
       </c>
       <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -3104,25 +3104,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1016/j.fuel.2024.131111</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.000856731</v>
+        <v>0.118529</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4805</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4925</v>
+        <v>0.971</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5755</v>
+        <v>0.9255</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
@@ -3131,30 +3131,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1016/j.cattod.2020.05.049</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.828627</v>
+        <v>0.549488</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="G32" t="n">
-        <v>0.973</v>
+        <v>0.9015</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
@@ -3163,44 +3163,44 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1021/acscatal.0c05628 | 50 bar | H2/CO2 4 | 21 NL/g/h</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acscatal.0c05628</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.57546</v>
+        <v>0.531343</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3209,16 +3209,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.167776</v>
+        <v>0.216698</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>0.982</v>
+        <v>0.8885</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
@@ -3227,30 +3227,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.aaz2060</t>
+          <t>10.1021/acscatal.5c05984</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.115626</v>
+        <v>0.0817657</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.9255</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9605</v>
+        <v>0.857</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
@@ -3259,12 +3259,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3273,48 +3273,48 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.0501492</v>
+        <v>2.9939</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0.994</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9165</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9825</v>
+        <v>0.8005</v>
       </c>
       <c r="H36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acs.energyfuels.6c02662</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.0354367</v>
+        <v>0.354294</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.9895</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9885</v>
+        <v>0.838</v>
       </c>
       <c r="G37" t="n">
-        <v>0.843</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -3323,62 +3323,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1021/acscatal.6c01275 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acscatal.6c01275</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.334351</v>
+        <v>0.0738813</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9825</v>
       </c>
       <c r="F38" t="n">
-        <v>0.974</v>
+        <v>0.859</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8305</v>
+        <v>0.6875</v>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10.1016/j.cattod.2020.05.049</t>
+          <t>10.1016/j.jcat.2012.05.020</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.0138623</v>
+        <v>0.376425</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.972</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9235</v>
+        <v>0.8415</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8115</v>
+        <v>0.703</v>
       </c>
       <c r="H39" t="b">
         <v>0</v>
@@ -3387,30 +3387,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+          <t>10.1016/j.apcata.2018.04.036 | 30 bar | H2/CO2 3 | 2.4 NL/g/h</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10.1021/acs.iecr.7b01464</t>
+          <t>10.1016/j.apcata.2018.04.036</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.013812</v>
+        <v>0.785093</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9595</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9535</v>
+        <v>0.822</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8285</v>
+        <v>0.645</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
@@ -3419,62 +3419,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10.1039/c2cy20604h</t>
+          <t>10.1021/acs.iecr.6c02734</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.116837</v>
+        <v>0.532547</v>
       </c>
       <c r="E41" t="n">
-        <v>0.992</v>
+        <v>0.954</v>
       </c>
       <c r="F41" t="n">
-        <v>0.881</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>0.737</v>
+        <v>0.699</v>
       </c>
       <c r="H41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.5c05984</t>
+          <t>10.1039/c2cy20604h</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.0175227</v>
+        <v>0.12945</v>
       </c>
       <c r="E42" t="n">
-        <v>0.954</v>
+        <v>0.951</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.8395</v>
       </c>
       <c r="G42" t="n">
-        <v>0.796</v>
+        <v>0.727</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -3483,94 +3483,94 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+          <t>10.1021/acscatal.1c03170 | 30 bar | H2/CO2 3 | 60 NL/g/h</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10.1039/c6ra28305e</t>
+          <t>10.1021/acscatal.1c03170</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.012303</v>
+        <v>0.628244</v>
       </c>
       <c r="E43" t="n">
-        <v>0.802</v>
+        <v>0.95</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6065</v>
+        <v>0.783</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5085</v>
+        <v>0.6565</v>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10.1021/acscatal.9b03305</t>
+          <t>10.1038/s41565-026-02135-y</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.00625936</v>
+        <v>0.400722</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6695</v>
+        <v>0.9295</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7065</v>
+        <v>0.8165</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7725</v>
+        <v>0.776</v>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>no_limit</t>
+          <t>inlet_limited</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10.1126/sciadv.abi6012</t>
+          <t>10.1021/acscatal.6c02907</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.000191829</v>
+        <v>0.07576919999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5125</v>
+        <v>0.9145</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5135</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.473</v>
+        <v>0.9055</v>
       </c>
       <c r="H45" t="b">
         <v>0</v>
@@ -3579,32 +3579,1056 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.0466421</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10.1007/s11426-026-3904-1 | 20 bar | H2/CO2 3 | 6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>10.1007/s11426-026-3904-1</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.00564525</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.00633792</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.6635</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6955</v>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 36 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0693766</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.543233</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.5215</v>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0202078</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.6995</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.00293911</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5235</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>inlet_limited</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.000856731</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.4935</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>no_limit</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.828627</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 2.5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.677878</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.57546</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.334351</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.167776</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aaz2060 | 50 bar | H2/CO2 3.04 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aaz2060</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.115626</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.0696623</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.0501492</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.03988</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.9945000000000001</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="H62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.0354367</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.9735</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01464 | 30 bar | H2/CO2 3.03 | 0.873 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.7b01464</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.013812</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9985000000000001</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="H64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.0138623</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.7955</v>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 4000 h-1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.116837</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.8804999999999999</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10.1021/acs.iecr.6c02734</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.0362971</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.0175227</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 1 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.134765</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.00889676</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="H70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.012303</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.8225</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="H71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.00383384</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="H72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.008147669999999999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="H73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.00625936</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6745</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.7705</v>
+      </c>
+      <c r="H74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0122249</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662 | 30 bar | H2/CO2 5 | 18 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>10.1021/acs.energyfuels.6c02662</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.0174511</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="H76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 8 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.000191829</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="H77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
         <is>
           <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>10.1016/j.fuel.2024.131111</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D78" t="n">
         <v>0.00163138</v>
       </c>
-      <c r="E46" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.2325</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.1245</v>
-      </c>
-      <c r="H46" t="b">
+      <c r="E78" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="H78" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3736,20 +4760,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7</v>
+        <v>0.6172839506172839</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.primary)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.primary)</t>
         </is>
       </c>
     </row>
@@ -3775,20 +4799,20 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.375</v>
+        <v>0.308641975308642</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.primary)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.primary)</t>
         </is>
       </c>
     </row>
@@ -3815,20 +4839,20 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>0.65625</v>
+        <v>0.589041095890411</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.without_bansode)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.without_bansode)</t>
         </is>
       </c>
     </row>
@@ -3855,20 +4879,20 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.without_bansode)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.without_bansode)</t>
         </is>
       </c>
     </row>
@@ -3895,20 +4919,20 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="G8" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.63125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.all_entries_inlet_limit / all_entries)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/all_entries/summary.json (S6/S5.combined)</t>
         </is>
       </c>
     </row>
@@ -3935,20 +4959,20 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4216867469879518</v>
+        <v>0.360248447204969</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>analysis/meoh_literature_inversion_2026_10_05/summary.json (variants.all_entries_inlet_limit / all_entries)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/all_entries/summary.json (S6/S5.combined)</t>
         </is>
       </c>
     </row>
@@ -3975,20 +4999,20 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.closure_ge95)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.closure_ge95)</t>
         </is>
       </c>
     </row>
@@ -4015,20 +5039,20 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.36</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.closure_ge95)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.closure_ge95)</t>
         </is>
       </c>
     </row>
@@ -4055,20 +5079,20 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="H12" t="n">
-        <v>0.65</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.low)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/selectivity_split/selectivity_split.json (S6/S5.low)</t>
         </is>
       </c>
     </row>
@@ -4095,20 +5119,20 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.35</v>
+        <v>0.2839506172839506</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.low)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/selectivity_split/selectivity_split.json (S6/S5.low)</t>
         </is>
       </c>
     </row>
@@ -4135,20 +5159,20 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H14" t="n">
-        <v>0.725</v>
+        <v>0.6790123456790124</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.high)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/selectivity_split/selectivity_split.json (S6/S5.high)</t>
         </is>
       </c>
     </row>
@@ -4175,20 +5199,20 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H15" t="n">
-        <v>0.45</v>
+        <v>0.4567901234567901</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (selectivity_split.S6/S5.high)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/selectivity_split/selectivity_split.json (S6/S5.high)</t>
         </is>
       </c>
     </row>
@@ -4215,20 +5239,20 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7</v>
+        <v>0.691358024691358</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.inert_co)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.inert_co)</t>
         </is>
       </c>
     </row>
@@ -4255,20 +5279,20 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H17" t="n">
-        <v>0.525</v>
+        <v>0.5802469135802469</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (frozen_columns.S6/S5.inert_co)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/summary.json (S6/S5.inert_co)</t>
         </is>
       </c>
     </row>
@@ -4295,20 +5319,20 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H18" t="n">
-        <v>0.625</v>
+        <v>0.5802469135802469</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (catalyst_cost.S6/S5.variants.composition_3y)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/catalyst_cost/catalyst_cost.json (S6/S5.variants.composition_3y)</t>
         </is>
       </c>
     </row>
@@ -4335,20 +5359,20 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>analysis/meoh_s6_robustness_2026_10_13/results.json (catalyst_cost.S6/S5.variants.composition_3y)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/catalyst_cost/catalyst_cost.json (S6/S5.variants.composition_3y)</t>
         </is>
       </c>
     </row>
@@ -4375,20 +5399,20 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F20" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H20" t="n">
-        <v>0.575</v>
+        <v>0.5679012345679012</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>analysis/verify_2026_10_12_s6_conversion/s6_conversion_summary.json / analysis/meoh_literature_inversion_2026_10_05/conversion_sensitivity_summary.json (printed|cost_f0.95)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/conversion_s6/s6_conversion_summary.json / conversion_s5/conversion_sensitivity_summary.json (printed|cost_f0.95)</t>
         </is>
       </c>
     </row>
@@ -4415,20 +5439,20 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>0.35</v>
+        <v>0.382716049382716</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>analysis/verify_2026_10_12_s6_conversion/s6_conversion_summary.json / analysis/meoh_literature_inversion_2026_10_05/conversion_sensitivity_summary.json (printed|cost_f0.95)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/conversion_s6/s6_conversion_summary.json / conversion_s5/conversion_sensitivity_summary.json (printed|cost_f0.95)</t>
         </is>
       </c>
     </row>

--- a/source_data/SourceData_EDFig3.xlsx
+++ b/source_data/SourceData_EDFig3.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="f" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -592,6 +593,42 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>panel f</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>analysis/meoh_catalyst_level_robustness_2026_10_24/groups_noise_raised.csv, groups_noise_lab.csv, summary_noise_*.json; cost gap from analysis/meoh_catalyst_level_2026_10_19/groups_catalyst_level_conversion_raised.csv, groups_catalyst_level.csv</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>constants drawn on panel f</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>analysis/meoh_catalyst_level_robustness_2026_10_24/groups_noise_raised.csv,</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5459,4 +5496,1377 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>panel f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_catalyst_level_robustness_2026_10_24/groups_noise_raised.csv, groups_noise_lab.csv, summary_noise_*.json; cost gap from analysis/meoh_catalyst_level_2026_10_19/groups_catalyst_level_conversion_raised.csv, groups_catalyst_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>gap</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>p_changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10.1016/j.jes.2023.05.010</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.260292</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06647 | 50 bar | H2/CO2 3 | 9 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06647</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.207087</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.200049</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-72876-w | 20 bar | H2/CO2 3 | 450 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-72876-w</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.190547</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 4 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.144732</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01275 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01275</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.119568</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.112073</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0585369</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0120959</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9675</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780 | 30 bar | H2/CO2 4 | 40 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06780</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0007154</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9565</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.1c03170 | 30 bar | H2/CO2 3 | 60 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.1c03170</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.00684566</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0614462</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x | 50 bar | H2/CO2 3 | 1.5 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10.1038/s41557-026-02104-x</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.00303501</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0131874</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.787</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2.40437e-06</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6895</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.238666</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6495</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0350789</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.593</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10.1039/c5cy00372e | 50 bar | H2/CO2 3.04 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10.1039/c5cy00372e</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.00390395</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5575</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.00293911</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.552</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0147289</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>more_catalyst</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 5 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.00324908</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.426</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 100 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.57562</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 2 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.364174</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10.1016/j.jes.2023.05.010 | 30 bar | H2/CO2 4 | 18000 h-1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>10.1016/j.jes.2023.05.010</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.23079</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842 | 30 bar | H2/CO2 3 | 48 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c04842</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.178319</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b03305</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.144612</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.133089</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c06714</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0853284</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012 | 40 bar | H2/CO2 3 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.abi6012</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0365433</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e | 30 bar | H2/CO2 3 | 3600 h-1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10.1039/c6ra28305e</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0264893</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111 | 40 bar | H2/CO2 5 | 12 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2024.131111</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.118529</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049 | 41 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>10.1016/j.cattod.2020.05.049</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.549488</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987 | 14 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c03987</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.10111</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01275 | 50 bar | H2/CO2 3 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c01275</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0738813</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9825</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2012.05.020 | 30 bar | H2/CO2 3 | 13.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10.1016/j.jcat.2012.05.020</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.376425</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984 | 100 bar | H2/CO2 4 | 10 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.5c05984</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0667758</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.972</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.1c03170 | 30 bar | H2/CO2 3 | 60 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.1c03170</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.628244</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10.1038/s41565-026-02135-y</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.400722</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9295</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 20 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.07576919999999999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.825</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041 | 50 bar | H2/CO2 4 | 24 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10.1126/sciadv.aea7041</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.376472</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7865</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 360 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0804754</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10.1007/s11426-026-3904-1 | 20 bar | H2/CO2 3 | 6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10.1007/s11426-026-3904-1</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.00564525</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b01869 | 50 bar | H2/CO2 4 | 24000 h-1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.9b01869</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.0441059</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974 | 20 bar | H2/CO2 3 | 3.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>10.1002/cctc.202000974</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.00633792</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5935</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907 | 10 bar | H2/CO2 3 | 30 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>10.1021/acscatal.6c02907</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.09116009999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5565</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h | 30 bar | H2/CO2 3.8 | 10.6 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>10.1039/c2cy20604h</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0202078</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.537</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>laboratory_conversion</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927 | 20 bar | H2/CO2 3 | 2.4 NL/g/h</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10.1016/j.fuel.2023.127927</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.00293911</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.5235</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>constants drawn on panel f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_catalyst_level_robustness_2026_10_24/groups_noise_raised.csv,</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>more_catalyst.observed</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>more_catalyst.groups</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>more_catalyst.mean</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>21.2145</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>more_catalyst.q025</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>more_catalyst.q975</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>more_catalyst.kept90</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>more_catalyst.kept50</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>more_catalyst.gt5</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>more_catalyst.gt5_kept90</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.observed</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.groups</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.mean</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>25.147</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.q025</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.q975</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.kept90</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.kept50</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.gt5</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>laboratory_conversion.gt5_kept90</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>